--- a/AI云业务/客户结算/山河（BID）云业务消耗费用.xlsx
+++ b/AI云业务/客户结算/山河（BID）云业务消耗费用.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="腾讯云" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿里云" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="腾讯云" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="阿里云" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -477,30 +477,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>实际消耗（￥）</t>
+          <t>币种</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>实际消耗（原币）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>服务费比例</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>服务费金额（￥）</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>结算总金额（￥）</t>
+          <t>服务费金额（原币）</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>结算总金额（原币）</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>服务费是否支付</t>
         </is>
@@ -522,23 +527,28 @@
           <t>hehegongsi3</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>954235.0600000001</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>954235.0600000001</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
@@ -560,21 +570,26 @@
           <t>北京山河聚量科技有限公司</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>132411.49</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2648.23</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>135059.72</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
@@ -596,23 +611,28 @@
           <t>hehegongsi3</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>623412.65</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>623412.65</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
@@ -634,21 +654,26 @@
           <t>北京山河聚量科技有限公司</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>190020.37</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>3800.41</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>193820.78</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
@@ -670,23 +695,28 @@
           <t>hehegongsi3</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>792183.1899999999</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>792183.1899999999</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
@@ -708,21 +738,26 @@
           <t>北京山河聚量科技有限公司</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>142932.83</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2858.66</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>145791.49</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
@@ -734,13 +769,13 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2835195.59</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>9307.299999999999</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2844502.89</v>
       </c>
     </row>
@@ -765,7 +800,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -926,7 +960,6 @@
         <v>145791.49</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
